--- a/INVENTARIOS DD PAJAN.xlsx
+++ b/INVENTARIOS DD PAJAN.xlsx
@@ -2707,10 +2707,8 @@
         </is>
       </c>
       <c r="B12" s="43" t="n"/>
-      <c r="C12" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="43" t="n">
+        <v>3</v>
       </c>
       <c r="D12" s="146" t="n"/>
       <c r="E12" s="133" t="n"/>
@@ -3253,13 +3251,11 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>RADIO 752TSZ3759 COMPLETA PARA ADMINISTRADORA</t>
+          <t xml:space="preserve">OTROS: </t>
         </is>
       </c>
       <c r="B40" s="44" t="n"/>
-      <c r="C40" s="43" t="n">
-        <v>1</v>
-      </c>
+      <c r="C40" s="43" t="n"/>
       <c r="D40" s="146" t="n"/>
       <c r="E40" s="133" t="n"/>
       <c r="F40" s="133" t="n"/>
